--- a/data/review/review_needed.xlsx
+++ b/data/review/review_needed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T530"/>
+  <dimension ref="A1:T549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4693,35 +4693,39 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>full_meal</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>cafe_with_food; coffee_shop</t>
+          <t>cafe_with_food; coffee_shop; pizzeria</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No web evidence available. OSM record only lists the venue as a cafe with no indication of food offerings or cuisine. Name does not strongly suggest a specific cuisine or food specialty.</t>
+          <t>No web evidence available. OSM record only lists the venue as a cafe with no indication of food offerings or cuisine. Name does not strongly suggest a specific cuisine or food specialty. Overture Maps category match: pizza_restaurant (confidence 0.77, name match 1.00)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (https://rondo.md)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7808,20 +7812,24 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>coffee_shop</t>
+          <t>coffee_shop; pizzeria</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>OSM tags the venue as a coffee shop with no additional food service details. No web evidence confirms the availability of savory meals or food items beyond drinks.</t>
+          <t>OSM tags the venue as a coffee shop with no additional food service details. No web evidence confirms the availability of savory meals or food items beyond drinks. Overture Maps category match: pizza_restaurant (confidence 0.36, name match 1.00)</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
@@ -11035,31 +11043,39 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>No web evidence available. OSM tags indicate Japanese cuisine, but no official menu, website, or social media content confirms actual food offerings or cuisine. Name 'Vasabi' is suggestive but not conclusive.</t>
+          <t>No web evidence available. OSM tags indicate Japanese cuisine, but no official menu, website, or social media content confirms actual food offerings or cuisine. Name 'Vasabi' is suggestive but not conclusive. Overture Maps category match: sushi_restaurant (confidence 0.84, name match 1.00)</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (www.vasabi.md)</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -11089,31 +11105,39 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>kebab_shop</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>kebab</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>No web evidence available to confirm food offerings or menu content. OSM tag 'cuisine: turkish' is not sufficient to establish cuisine country or region, nor to infer food specialties without explicit menu or official source confirmation.</t>
+          <t>No web evidence available to confirm food offerings or menu content. OSM tag 'cuisine: turkish' is not sufficient to establish cuisine country or region, nor to infer food specialties without explicit menu or official source confirmation. Overture Maps category match: doner_kebab (confidence 0.77, name match 1.00)</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other</t>
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
@@ -11321,31 +11345,39 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>OSM record lists cuisine as 'italian' but provides no menu, website, or additional evidence to confirm food offerings or cuisine authenticity. No web evidence available to validate claims.</t>
+          <t>OSM record lists cuisine as 'italian' but provides no menu, website, or additional evidence to confirm food offerings or cuisine authenticity. No web evidence available to validate claims. Overture Maps category match: pizza_restaurant (confidence 1.00, name match 1.00)</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (http://www.mipiace.md/)</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -11603,31 +11635,39 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>OSM record lists cuisine as 'italian' but provides no menu, website, or additional evidence to confirm the actual food offerings or cuisine authenticity. Name 'Casa Della Pizza' is suggestive but not sufficient alone to confirm Italian cuisine or food specialties without corroborating evidence.</t>
+          <t>OSM record lists cuisine as 'italian' but provides no menu, website, or additional evidence to confirm the actual food offerings or cuisine authenticity. Name 'Casa Della Pizza' is suggestive but not sufficient alone to confirm Italian cuisine or food specialties without corroborating evidence. Overture Maps category match: pizza_restaurant (confidence 0.99, name match 1.00)</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (http://casadellapizza.md/)</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -12101,31 +12141,39 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>OSM record names the venue as 'Storno Pasta &amp; Pizza' and tags it with Italian cuisine, but no web evidence is available to confirm actual menu content, food offerings, or cultural origin. Name alone does not constitute sufficient evidence for cuisine classification.</t>
+          <t>OSM record names the venue as 'Storno Pasta &amp; Pizza' and tags it with Italian cuisine, but no web evidence is available to confirm actual menu content, food offerings, or cultural origin. Name alone does not constitute sufficient evidence for cuisine classification. Overture Maps category match: pizza_restaurant (confidence 0.96, name match 1.00)</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (http://www.storno.md/)</t>
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
@@ -23389,31 +23437,39 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr"/>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>No web evidence available. OSM record lists the venue as a cafe with no cuisine or menu details. The name 'Flame RestoBar' does not explicitly indicate food offerings or specific cuisines. Without official menu or website, food service scope and cuisine cannot be determined.</t>
+          <t>No web evidence available. OSM record lists the venue as a cafe with no cuisine or menu details. The name 'Flame RestoBar' does not explicitly indicate food offerings or specific cuisines. Without official menu or website, food service scope and cuisine cannot be determined. Overture Maps category match: sushi_restaurant (confidence 0.81, name match 0.60)</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>osm</t>
+          <t>osm; other (http://www.kamii.md/)</t>
         </is>
       </c>
       <c r="N402" t="inlineStr"/>
@@ -29031,12 +29087,12 @@
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -29046,24 +29102,24 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>fast_food; dessert_shop</t>
+          <t>dessert_shop; fast_food; pizzeria</t>
         </is>
       </c>
       <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr">
         <is>
-          <t>ice_cream</t>
+          <t>ice_cream; pizza</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>Web evidence shows Andy's Express is a frozen custard chain offering only frozen custard with toppings, indicating dessert-only service. No evidence of savory meals or full meal options. Venue is tagged as fast_food in OSM, but no cuisine or food service details are provided.</t>
+          <t>Web evidence shows Andy's Express is a frozen custard chain offering only frozen custard with toppings, indicating dessert-only service. No evidence of savory meals or full meal options. Venue is tagged as fast_food in OSM, but no cuisine or food service details are provided. Overture Maps category match: pizza_restaurant (confidence 0.77, name match 1.00)</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>osm; other (https://www.eatandys.com/); other (https://www.eatandys.com/full-menu/)</t>
+          <t>osm; other (https://www.eatandys.com/); other (https://www.eatandys.com/full-menu/); other (https://andys.md)</t>
         </is>
       </c>
       <c r="N505" t="inlineStr"/>
@@ -30468,6 +30524,1184 @@
       <c r="S530" t="inlineStr"/>
       <c r="T530" t="inlineStr"/>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>overture/45d71e7d-fa49-4db6-ab8f-2c4399d33e08</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Sushi Master Crab</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.27) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr"/>
+      <c r="O531" t="inlineStr"/>
+      <c r="P531" t="inlineStr"/>
+      <c r="Q531" t="n">
+        <v>46.95496466</v>
+      </c>
+      <c r="R531" t="n">
+        <v>28.77038206</v>
+      </c>
+      <c r="S531" t="inlineStr"/>
+      <c r="T531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>overture/9a05080d-bfce-45e9-950d-9826833f9e8a</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Sushi Kaif</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.13) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>other (http://sushi-kaif.md/)</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr"/>
+      <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="n">
+        <v>46.97703579</v>
+      </c>
+      <c r="R532" t="n">
+        <v>28.85799726</v>
+      </c>
+      <c r="S532" t="inlineStr"/>
+      <c r="T532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>overture/27b5c063-e418-4dfa-ab81-c9074c66f4b5</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Sushi-Set</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr"/>
+      <c r="D533" t="inlineStr"/>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.35) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>other (http://sushi-set.md/)</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr"/>
+      <c r="O533" t="inlineStr"/>
+      <c r="P533" t="inlineStr"/>
+      <c r="Q533" t="n">
+        <v>46.99455</v>
+      </c>
+      <c r="R533" t="n">
+        <v>28.85398</v>
+      </c>
+      <c r="S533" t="inlineStr"/>
+      <c r="T533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>overture/7a6ed616-25ef-4c96-b7d9-5e4b4573921e</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Speedy Pizza</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Overture Maps category: pizza_restaurant (confidence 0.46) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>other (http://www.speedypizza.md/)</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr"/>
+      <c r="O534" t="inlineStr"/>
+      <c r="P534" t="inlineStr"/>
+      <c r="Q534" t="n">
+        <v>46.99036305</v>
+      </c>
+      <c r="R534" t="n">
+        <v>28.85967617</v>
+      </c>
+      <c r="S534" t="inlineStr"/>
+      <c r="T534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>overture/26f9690c-2d49-4773-b4d2-0d7ad71f8dc7</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Artigiano - Pizzeria napolitana</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Overture Maps category: pizza_restaurant (confidence 0.38) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>other (http://www.artigiano.md/)</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr"/>
+      <c r="O535" t="inlineStr"/>
+      <c r="P535" t="inlineStr"/>
+      <c r="Q535" t="n">
+        <v>47.04266104</v>
+      </c>
+      <c r="R535" t="n">
+        <v>28.76988084</v>
+      </c>
+      <c r="S535" t="inlineStr"/>
+      <c r="T535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>overture/44b67d22-f8ac-4511-85eb-06c595dbf6ee</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Kebab Point</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>kebab_shop</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>kebab</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>Overture Maps category: doner_kebab (confidence 0.43) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>other (https://kebabpointmoldova.business.site/)</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr"/>
+      <c r="O536" t="inlineStr"/>
+      <c r="P536" t="inlineStr"/>
+      <c r="Q536" t="n">
+        <v>47.04407103</v>
+      </c>
+      <c r="R536" t="n">
+        <v>28.7696625</v>
+      </c>
+      <c r="S536" t="inlineStr"/>
+      <c r="T536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>overture/6141f009-f84b-4fe8-8d02-e90fd277c6d8</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Livrarea Sushi</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr"/>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.43) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>other (https://pandasushi.md)</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr"/>
+      <c r="O537" t="inlineStr"/>
+      <c r="P537" t="inlineStr"/>
+      <c r="Q537" t="n">
+        <v>47.05515</v>
+      </c>
+      <c r="R537" t="n">
+        <v>28.86588</v>
+      </c>
+      <c r="S537" t="inlineStr"/>
+      <c r="T537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>overture/36f798a9-c34d-421d-aa99-35d1f4f0831c</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>LuVi Sushi</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr"/>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.45) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>other (http://www.luvisushi.md/)</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr"/>
+      <c r="O538" t="inlineStr"/>
+      <c r="P538" t="inlineStr"/>
+      <c r="Q538" t="n">
+        <v>47.05735</v>
+      </c>
+      <c r="R538" t="n">
+        <v>28.89246</v>
+      </c>
+      <c r="S538" t="inlineStr"/>
+      <c r="T538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>overture/235447c8-952e-44b8-a9f7-eacc7f7933a1</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>PizzaSi</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr"/>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>Overture Maps category: pizza_restaurant (confidence 0.44) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr"/>
+      <c r="O539" t="inlineStr"/>
+      <c r="P539" t="inlineStr"/>
+      <c r="Q539" t="n">
+        <v>47.03033272</v>
+      </c>
+      <c r="R539" t="n">
+        <v>28.83655134</v>
+      </c>
+      <c r="S539" t="inlineStr"/>
+      <c r="T539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>overture/a4bd3207-258c-47ed-a89f-448e68f74949</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Oishii – Sushi &amp; Wok</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr"/>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.43) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>other (https://oishii.md/)</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr"/>
+      <c r="O540" t="inlineStr"/>
+      <c r="P540" t="inlineStr"/>
+      <c r="Q540" t="n">
+        <v>47.02501624</v>
+      </c>
+      <c r="R540" t="n">
+        <v>28.84157348</v>
+      </c>
+      <c r="S540" t="inlineStr"/>
+      <c r="T540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>overture/8628a103-c714-48e9-baaf-2bbe298de079</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Takumi.md</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr"/>
+      <c r="D541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.28) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>other (http://www.takumi.md/)</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr"/>
+      <c r="O541" t="inlineStr"/>
+      <c r="P541" t="inlineStr"/>
+      <c r="Q541" t="n">
+        <v>47.0247187</v>
+      </c>
+      <c r="R541" t="n">
+        <v>28.8325092</v>
+      </c>
+      <c r="S541" t="inlineStr"/>
+      <c r="T541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>overture/d29c0e96-843a-4aac-b12b-cc750c9cf601</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Grill Star</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr"/>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>burger_shop</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>Overture Maps category: burger_restaurant (confidence 0.38) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>other (https://fb.me/Grill.Star.Burger)</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr"/>
+      <c r="O542" t="inlineStr"/>
+      <c r="P542" t="inlineStr"/>
+      <c r="Q542" t="n">
+        <v>47.02324327</v>
+      </c>
+      <c r="R542" t="n">
+        <v>28.8365808</v>
+      </c>
+      <c r="S542" t="inlineStr"/>
+      <c r="T542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>overture/1c693df2-095a-4183-b7b8-803583ecd8d3</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Cucurigo</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>burger_shop</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>Overture Maps category: burger_restaurant (confidence 0.35) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>other (http://www.cucurigo.md/)</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr"/>
+      <c r="O543" t="inlineStr"/>
+      <c r="P543" t="inlineStr"/>
+      <c r="Q543" t="n">
+        <v>47.03239652</v>
+      </c>
+      <c r="R543" t="n">
+        <v>28.84462418</v>
+      </c>
+      <c r="S543" t="inlineStr"/>
+      <c r="T543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>overture/33fd1f8b-b99f-4ab0-9f69-46c146013563</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Kyoto Sushi</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr"/>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.25) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>other (https://kyotosushi.md/)</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr"/>
+      <c r="O544" t="inlineStr"/>
+      <c r="P544" t="inlineStr"/>
+      <c r="Q544" t="n">
+        <v>47.03739408</v>
+      </c>
+      <c r="R544" t="n">
+        <v>28.83054021</v>
+      </c>
+      <c r="S544" t="inlineStr"/>
+      <c r="T544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>overture/af44eda3-91ba-4de8-9074-24e2bfac4fab</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Sushi Pop</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr"/>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.31) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr"/>
+      <c r="O545" t="inlineStr"/>
+      <c r="P545" t="inlineStr"/>
+      <c r="Q545" t="n">
+        <v>47.0212664</v>
+      </c>
+      <c r="R545" t="n">
+        <v>28.80564065</v>
+      </c>
+      <c r="S545" t="inlineStr"/>
+      <c r="T545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>overture/ec8338b4-c1ec-46ed-a9c9-3c73c2f01dff</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Kebab Mania</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr"/>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>kebab_shop</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>kebab</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>Overture Maps category: doner_kebab (confidence 0.12) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr"/>
+      <c r="O546" t="inlineStr"/>
+      <c r="P546" t="inlineStr"/>
+      <c r="Q546" t="n">
+        <v>47.0193731</v>
+      </c>
+      <c r="R546" t="n">
+        <v>28.84544202</v>
+      </c>
+      <c r="S546" t="inlineStr"/>
+      <c r="T546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>overture/af7c632d-1c19-4ac5-a50c-8fa4b6cb6215</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>kayasushi.md</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr"/>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>sushi_restaurant</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>sushi</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>Overture Maps category: sushi_restaurant (confidence 0.46) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>other (https://kayasushi.md/ro)</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr"/>
+      <c r="O547" t="inlineStr"/>
+      <c r="P547" t="inlineStr"/>
+      <c r="Q547" t="n">
+        <v>47.01832</v>
+      </c>
+      <c r="R547" t="n">
+        <v>28.84342</v>
+      </c>
+      <c r="S547" t="inlineStr"/>
+      <c r="T547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>overture/be0efb14-a8a0-4324-9ebe-21807d398fa1</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Donerci</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr"/>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>limited_meal</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>kebab_shop</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>kebab</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>Overture Maps category: doner_kebab (confidence 0.24) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>other (http://donerci.md/)</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr"/>
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="inlineStr"/>
+      <c r="Q548" t="n">
+        <v>47.01466761</v>
+      </c>
+      <c r="R548" t="n">
+        <v>28.8559299</v>
+      </c>
+      <c r="S548" t="inlineStr"/>
+      <c r="T548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>overture/e30a8427-f4d4-41bd-9d6c-85bd69fd7ac7</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Amalfi By Telemar</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>full_meal</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>pizzeria</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>pizza</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>Overture Maps category: pizza_restaurant (confidence 0.27) Not present in the original OSM-derived venue list.</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>other (https://telemar.md/ro/product-category/produse-italia/)</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr"/>
+      <c r="O549" t="inlineStr"/>
+      <c r="P549" t="inlineStr"/>
+      <c r="Q549" t="n">
+        <v>47.00921</v>
+      </c>
+      <c r="R549" t="n">
+        <v>28.88008</v>
+      </c>
+      <c r="S549" t="inlineStr"/>
+      <c r="T549" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
